--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
   <si>
     <t>Filename</t>
   </si>
@@ -808,652 +808,688 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9959,0.0002,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0155,0.0003,0.0014,0.9922</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0631,0.0003,0.0003,0.9848</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9963,0.0001,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.0032,0.9983</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.3144,0.0001,0.0006,0.8907</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9761,0.0015,0.0104,0.0003</t>
+  </si>
+  <si>
+    <t>0.6572,0.0005,0.4125,0.0003</t>
+  </si>
+  <si>
+    <t>0.8664,0.0029,0.1386,0.0001</t>
+  </si>
+  <si>
+    <t>0.0082,0.0028,0.9899,0.0004</t>
+  </si>
+  <si>
+    <t>0.5734,0.0017,0.4849,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0035,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0020,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9967,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.8628,0.0005,0.1473,0.0011</t>
+  </si>
+  <si>
+    <t>0.3564,0.0014,0.6882,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0070,0.0011,0.9928,0.0001</t>
+  </si>
+  <si>
+    <t>0.7922,0.0006,0.3056,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0005,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0006</t>
+  </si>
+  <si>
+    <t>0.8984,0.1084,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9746,0.0185,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0021,0.9996,0.0006</t>
+  </si>
+  <si>
+    <t>0.1458,0.6538,0.0496,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.8734,0.0018,0.1046,0.0024</t>
+  </si>
+  <si>
+    <t>0.9391,0.0674,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9980,0.0069,0.0000</t>
+  </si>
+  <si>
+    <t>0.0051,0.3922,0.8650,0.0010</t>
+  </si>
+  <si>
+    <t>0.0161,0.0092,0.9731,0.0037</t>
+  </si>
+  <si>
+    <t>0.0040,0.0087,0.9893,0.0004</t>
+  </si>
+  <si>
+    <t>0.0896,0.0001,0.9446,0.0002</t>
+  </si>
+  <si>
+    <t>0.0088,0.0381,0.9857,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9949,0.0638,0.0002</t>
+  </si>
+  <si>
+    <t>0.0160,0.0081,0.9784,0.0003</t>
+  </si>
+  <si>
+    <t>0.0879,0.0021,0.0034,0.9557</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9970,0.0038,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0096,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0071,0.2275,0.9524,0.0000</t>
+  </si>
+  <si>
+    <t>0.0538,0.0007,0.9629,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0358,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0020,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0240,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0039,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.9032,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0252,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0078,0.9955,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.9961,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.9983,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0007,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.6542,0.0156,0.3086,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0071,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9911,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.1070,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9711,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0000,0.0205,0.9796</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.0004,0.9992</t>
+  </si>
+  <si>
+    <t>0.1254,0.0000,0.0000,0.9878</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0072,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9718,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9727,0.9813,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9793,0.9870,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9927,0.8824,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.1557,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0089,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.9833,0.0007,0.0088,0.0002</t>
+  </si>
+  <si>
+    <t>0.0117,0.0007,0.9916,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9988,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.9942,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9681,0.0389,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.2621,0.0032,0.7109,0.0025</t>
+  </si>
+  <si>
+    <t>0.9921,0.0008,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9085,0.0056,0.0586,0.0006</t>
+  </si>
+  <si>
+    <t>0.4362,0.0011,0.5837,0.0021</t>
+  </si>
+  <si>
+    <t>0.0536,0.0183,0.0307,0.8543</t>
+  </si>
+  <si>
+    <t>0.0004,0.9979,0.0114,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9919,0.9955,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9080,0.0902,0.0041,0.0001</t>
+  </si>
+  <si>
+    <t>0.9009,0.1024,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.7484,0.7774,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.5241,0.9487,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0085,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0218,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0002,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0120,0.0049,0.9878,0.0004</t>
+  </si>
+  <si>
+    <t>0.9380,0.0002,0.0835,0.0002</t>
+  </si>
+  <si>
+    <t>0.9446,0.0107,0.0114,0.0007</t>
+  </si>
+  <si>
+    <t>0.4856,0.0000,0.0001,0.8928</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0038,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9888,0.8862,0.0000</t>
+  </si>
+  <si>
+    <t>0.5232,0.5142,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0441,0.9394,0.0158,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.0103,0.0014,0.0069,0.9893</t>
+  </si>
+  <si>
+    <t>0.0007,0.0834,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.9877,0.0000,0.0010,0.0130</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.0667,0.9113,0.0130,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.2741,0.6012,0.0198,0.0024</t>
+  </si>
+  <si>
+    <t>0.9945,0.0005,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0007,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9931,0.0047,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.3116,0.6978,0.0101,0.0001</t>
+  </si>
+  <si>
+    <t>0.2793,0.6660,0.0238,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.1908,0.9873,0.0001</t>
+  </si>
+  <si>
+    <t>0.9477,0.0615,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9904,0.0035,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0055,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0148,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9881,0.0046,0.0027,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0071,0.9914,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0168,0.3294,0.6854,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0081,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0016,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.2458,0.0011,0.7779,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.0012,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0184,0.0032,0.9779,0.0008</t>
+  </si>
+  <si>
+    <t>0.4022,0.0236,0.4786,0.0002</t>
+  </si>
+  <si>
+    <t>0.0088,0.6230,0.4818,0.0004</t>
+  </si>
+  <si>
+    <t>0.9562,0.0160,0.0097,0.0001</t>
+  </si>
+  <si>
+    <t>0.9284,0.0098,0.0258,0.0011</t>
+  </si>
+  <si>
+    <t>0.4125,0.0066,0.5870,0.0006</t>
+  </si>
+  <si>
+    <t>0.3124,0.7712,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.0225,0.9688,0.0121,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0070,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9881,0.0167,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0055,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9696,0.0174,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9828,0.0015,0.0067,0.0002</t>
+  </si>
+  <si>
+    <t>0.9769,0.0009,0.0108,0.0011</t>
+  </si>
+  <si>
+    <t>0.9931,0.0001,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.2847,0.0052,0.7636,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.0007,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0346,0.9949,0.0002</t>
+  </si>
+  <si>
+    <t>0.0178,0.0596,0.9340,0.0004</t>
+  </si>
+  <si>
+    <t>0.0516,0.0131,0.9093,0.0004</t>
+  </si>
+  <si>
+    <t>0.0107,0.3382,0.7639,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0006,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0041,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0023,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.2578,0.9942,0.0001</t>
+  </si>
+  <si>
+    <t>0.0852,0.6139,0.1763,0.0004</t>
+  </si>
+  <si>
+    <t>0.9003,0.0014,0.1001,0.0013</t>
+  </si>
+  <si>
+    <t>0.0029,0.0013,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0068,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8944,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.0013,0.9952,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0007,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0064,0.0019,0.9914,0.0005</t>
+  </si>
+  <si>
+    <t>0.2461,0.0035,0.7938,0.0007</t>
+  </si>
+  <si>
+    <t>0.8891,0.0010,0.1149,0.0005</t>
+  </si>
+  <si>
+    <t>0.9901,0.0003,0.0057,0.0001</t>
+  </si>
+  <si>
+    <t>0.9863,0.0126,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9116,0.0195,0.0331,0.0005</t>
-  </si>
-  <si>
-    <t>0.0267,0.0008,0.9803,0.0001</t>
-  </si>
-  <si>
-    <t>0.8377,0.0047,0.1633,0.0001</t>
-  </si>
-  <si>
-    <t>0.0153,0.0028,0.9820,0.0003</t>
-  </si>
-  <si>
-    <t>0.9640,0.0068,0.0121,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.9934,0.0064,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8878,0.0001,0.0540,0.0107</t>
-  </si>
-  <si>
-    <t>0.6221,0.0022,0.3483,0.0006</t>
-  </si>
-  <si>
-    <t>0.0043,0.0022,0.9946,0.0002</t>
-  </si>
-  <si>
-    <t>0.0372,0.0001,0.9790,0.0001</t>
-  </si>
-  <si>
-    <t>0.9765,0.0001,0.0283,0.0000</t>
-  </si>
-  <si>
-    <t>0.0185,0.0007,0.9878,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.7763,0.2551,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.9912,0.0021,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0038,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0051,0.9913,0.0048,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0004,0.0041,0.0008</t>
-  </si>
-  <si>
-    <t>0.3036,0.7483,0.0083,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9960,0.0252,0.0001</t>
-  </si>
-  <si>
-    <t>0.0559,0.5981,0.1903,0.0017</t>
-  </si>
-  <si>
-    <t>0.0041,0.0018,0.9928,0.0011</t>
-  </si>
-  <si>
-    <t>0.0037,0.0088,0.9924,0.0004</t>
-  </si>
-  <si>
-    <t>0.0059,0.0001,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.1296,0.9846,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0088,0.0027,0.9881,0.0004</t>
-  </si>
-  <si>
-    <t>0.0787,0.0086,0.0008,0.9480</t>
-  </si>
-  <si>
-    <t>0.0003,0.9988,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0103,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.5532,0.9679,0.0000</t>
-  </si>
-  <si>
-    <t>0.7258,0.0006,0.3359,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0008,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0045,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0007,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0010,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.4115,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.8807,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0025,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.9961,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.9985,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9730,0.0019,0.0209,0.0001</t>
-  </si>
-  <si>
-    <t>0.9923,0.0004,0.0040,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0016,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9928,0.9066,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.5775,0.0000</t>
-  </si>
-  <si>
-    <t>0.0080,0.0000,0.0008,0.9959</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0029,0.9992</t>
-  </si>
-  <si>
-    <t>0.1782,0.0000,0.0000,0.9811</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9985,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9964,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9681,0.9398,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9981,0.9610,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.3659,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9225,0.7480,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0044,0.0043,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0002,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0003,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9982,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9981,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9821,0.0241,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8430,0.0071,0.1039,0.0012</t>
-  </si>
-  <si>
-    <t>0.9748,0.0027,0.0074,0.0001</t>
-  </si>
-  <si>
-    <t>0.9235,0.0168,0.0246,0.0002</t>
-  </si>
-  <si>
-    <t>0.0784,0.0016,0.9192,0.0012</t>
-  </si>
-  <si>
-    <t>0.0305,0.0086,0.0239,0.9261</t>
-  </si>
-  <si>
-    <t>0.0005,0.9971,0.0173,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9954,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.6345,0.3687,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.9835,0.0141,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0009,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.8980,0.5894,0.0006</t>
-  </si>
-  <si>
-    <t>0.0047,0.1383,0.9605,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0041,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0059,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9941,0.0002,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.7136,0.0048,0.2939,0.0008</t>
-  </si>
-  <si>
-    <t>0.9932,0.0000,0.0055,0.0000</t>
-  </si>
-  <si>
-    <t>0.9613,0.0050,0.0164,0.0003</t>
-  </si>
-  <si>
-    <t>0.0364,0.0000,0.0002,0.9925</t>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.0295,0.9821,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.0015,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0080,0.0085,0.9825,0.0007</t>
+  </si>
+  <si>
+    <t>0.0116,0.0044,0.9810,0.0004</t>
+  </si>
+  <si>
+    <t>0.0621,0.0010,0.9611,0.0001</t>
+  </si>
+  <si>
+    <t>0.0135,0.0009,0.9869,0.0005</t>
+  </si>
+  <si>
+    <t>0.0610,0.0037,0.9193,0.0015</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.7986,0.0001,0.0158,0.1592</t>
+  </si>
+  <si>
+    <t>0.0063,0.0190,0.0002,0.9936</t>
+  </si>
+  <si>
+    <t>0.0987,0.0000,0.0009,0.9612</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.0000,0.9997</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9962,0.8974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0117,0.9865,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0443,0.9240,0.0265,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0119,0.0001,0.0012,0.9946</t>
-  </si>
-  <si>
-    <t>0.0048,0.0519,0.9845,0.0012</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0028,0.9902,0.0206,0.0002</t>
-  </si>
-  <si>
-    <t>0.9934,0.0007,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0002,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.3300,0.5607,0.0132,0.0011</t>
-  </si>
-  <si>
-    <t>0.8090,0.0258,0.1063,0.0002</t>
-  </si>
-  <si>
-    <t>0.9437,0.0537,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9787,0.0233,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.3890,0.5696,0.0221,0.0002</t>
-  </si>
-  <si>
-    <t>0.3026,0.6762,0.0170,0.0001</t>
-  </si>
-  <si>
-    <t>0.0322,0.0894,0.9165,0.0001</t>
-  </si>
-  <si>
-    <t>0.9390,0.0680,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9874,0.0070,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9526,0.0426,0.0049,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0083,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9746,0.0095,0.0073,0.0015</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0063,0.0032,0.9898,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0402,0.0320,0.9242,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0034,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0082,0.0017,0.9903,0.0003</t>
-  </si>
-  <si>
-    <t>0.0092,0.0017,0.9924,0.0001</t>
-  </si>
-  <si>
-    <t>0.8735,0.0185,0.0361,0.0036</t>
-  </si>
-  <si>
-    <t>0.5438,0.3222,0.0186,0.0001</t>
-  </si>
-  <si>
-    <t>0.1008,0.3419,0.3697,0.0002</t>
-  </si>
-  <si>
-    <t>0.9356,0.0298,0.0125,0.0002</t>
-  </si>
-  <si>
-    <t>0.9045,0.0014,0.0859,0.0017</t>
-  </si>
-  <si>
-    <t>0.0394,0.0263,0.9446,0.0004</t>
-  </si>
-  <si>
-    <t>0.9385,0.0739,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0097,0.9739,0.0396,0.0000</t>
-  </si>
-  <si>
-    <t>0.9917,0.0098,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0019,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8462,0.3254,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0010,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9851,0.0003,0.0043,0.0018</t>
-  </si>
-  <si>
-    <t>0.9443,0.0016,0.0487,0.0011</t>
-  </si>
-  <si>
-    <t>0.2796,0.0125,0.7172,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.1152,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0299,0.9934,0.0001</t>
-  </si>
-  <si>
-    <t>0.8304,0.0026,0.1390,0.0002</t>
-  </si>
-  <si>
-    <t>0.0045,0.1910,0.8971,0.0007</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0350,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.0987,0.1291,0.6594,0.0010</t>
-  </si>
-  <si>
-    <t>0.9631,0.0012,0.0254,0.0040</t>
-  </si>
-  <si>
-    <t>0.0365,0.0019,0.9709,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0013,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0766,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0009,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0010,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0013,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0022,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.9896,0.0001,0.0083,0.0000</t>
-  </si>
-  <si>
-    <t>0.9736,0.0003,0.0266,0.0004</t>
-  </si>
-  <si>
-    <t>0.9860,0.0008,0.0056,0.0009</t>
-  </si>
-  <si>
-    <t>0.9984,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.1910,0.9445,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0031,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0178,0.9886,0.0005</t>
-  </si>
-  <si>
-    <t>0.0053,0.0609,0.9572,0.0006</t>
-  </si>
-  <si>
-    <t>0.1471,0.0007,0.9095,0.0001</t>
-  </si>
-  <si>
-    <t>0.3124,0.0002,0.7569,0.0013</t>
-  </si>
-  <si>
-    <t>0.1622,0.0027,0.8153,0.0008</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.9791,0.0001,0.0118,0.0036</t>
-  </si>
-  <si>
-    <t>0.0037,0.0180,0.0004,0.9952</t>
-  </si>
-  <si>
-    <t>0.0323,0.0000,0.0013,0.9866</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0288,0.0092,0.0007,0.9828</t>
+    <t>0.9764,0.0028,0.0067,0.0041</t>
   </si>
 </sst>
 </file>
@@ -1839,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1853,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1867,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1881,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1895,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1909,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1923,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1937,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1951,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1965,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1979,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1993,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2007,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2018,10 +2054,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2035,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2049,7 +2085,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2063,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2077,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2091,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2105,7 +2141,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2119,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2133,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2147,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2158,10 +2194,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2175,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2189,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2203,7 +2239,7 @@
         <v>259</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2217,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2231,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2245,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2259,7 +2295,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2273,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2287,7 +2323,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2301,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2315,7 +2351,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2326,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2343,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2354,10 +2390,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2371,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2385,7 +2421,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2399,7 +2435,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2413,7 +2449,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2427,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2441,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2455,7 +2491,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2469,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2483,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2497,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2511,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2522,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2536,10 +2572,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2553,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2567,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2581,7 +2617,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2595,7 +2631,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2609,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2623,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2637,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2651,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2665,7 +2701,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>272</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2679,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2693,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2707,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2721,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2735,7 +2771,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2749,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2763,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2777,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2791,7 +2827,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2805,7 +2841,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2819,7 +2855,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2833,7 +2869,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2844,10 +2880,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2861,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2875,7 +2911,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2889,7 +2925,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2903,7 +2939,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2917,7 +2953,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2931,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2945,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2959,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2973,7 +3009,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2987,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3001,7 +3037,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3015,7 +3051,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3026,10 +3062,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3040,10 +3076,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3057,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3071,7 +3107,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3085,7 +3121,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>268</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3099,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3113,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3127,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3141,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3155,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3169,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3183,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3197,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3211,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3225,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3239,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3253,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3267,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3281,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3295,7 +3331,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3309,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3323,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3337,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3351,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>283</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3365,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3379,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3393,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3407,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3421,7 +3457,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3432,10 +3468,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3449,7 +3485,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3463,7 +3499,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3477,7 +3513,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3491,7 +3527,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3505,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3519,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3533,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3547,7 +3583,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3561,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3575,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3589,7 +3625,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3603,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3617,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3631,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>374</v>
+        <v>270</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3645,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>271</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3659,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3673,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>375</v>
+        <v>274</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3687,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3701,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3715,7 +3751,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3726,10 +3762,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3743,7 +3779,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3757,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3771,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3782,10 +3818,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3799,7 +3835,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3813,7 +3849,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3827,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3841,7 +3877,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3855,7 +3891,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3869,7 +3905,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>337</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3883,7 +3919,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3897,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3908,10 +3944,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D150" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3925,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>268</v>
+        <v>396</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3939,7 +3975,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3953,7 +3989,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3967,7 +4003,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3981,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>271</v>
+        <v>380</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3995,7 +4031,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4009,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4023,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4037,7 +4073,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4051,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4065,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4079,7 +4115,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4093,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4107,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4121,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4135,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4149,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>401</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4163,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4177,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4191,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>269</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4205,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4219,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4233,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4247,7 +4283,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4261,7 +4297,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4275,7 +4311,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4289,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4303,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4317,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4331,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4345,7 +4381,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4359,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4373,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4387,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4401,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4415,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4429,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4443,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4457,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4471,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4485,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4496,10 +4532,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4510,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4524,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4541,7 +4577,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4555,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4569,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4580,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4597,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4611,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4625,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4639,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4653,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4667,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4681,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4695,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4709,7 +4745,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4723,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4737,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4751,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4762,10 +4798,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4779,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4793,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4807,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4821,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4835,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4849,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4863,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4877,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4891,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4905,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4916,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4933,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4947,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4961,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4972,10 +5008,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4989,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5003,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5017,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5031,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5045,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5056,10 +5092,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5073,7 +5109,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5087,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5101,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5115,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5129,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5143,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>272</v>
+        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5157,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5171,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5185,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>465</v>
+        <v>352</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5199,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5213,7 +5249,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5227,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5241,7 +5277,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5255,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5269,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5283,7 +5319,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5297,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5311,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5325,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5339,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5353,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5367,7 +5403,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5381,7 +5417,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5392,10 +5428,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
